--- a/public/demo/namuna-katalog.xlsx
+++ b/public/demo/namuna-katalog.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="483">
   <si>
     <t>Наименование</t>
   </si>
@@ -335,6 +335,1131 @@
   </si>
   <si>
     <t>28000</t>
+  </si>
+  <si>
+    <t>Mix (gvozd) 100 mm</t>
+  </si>
+  <si>
+    <t>01101001001000000</t>
+  </si>
+  <si>
+    <t>dona</t>
+  </si>
+  <si>
+    <t>47500</t>
+  </si>
+  <si>
+    <t>Elektr kabeli VVG 3x2,5</t>
+  </si>
+  <si>
+    <t>metr</t>
+  </si>
+  <si>
+    <t>83500</t>
+  </si>
+  <si>
+    <t>Рис круглозерный 5кг</t>
+  </si>
+  <si>
+    <t>86000</t>
+  </si>
+  <si>
+    <t>G'isht pishgan M100</t>
+  </si>
+  <si>
+    <t>06901001002000000</t>
+  </si>
+  <si>
+    <t>72500</t>
+  </si>
+  <si>
+    <t>Un 1-nav 25 kg</t>
+  </si>
+  <si>
+    <t>01101001002000000</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>40500</t>
+  </si>
+  <si>
+    <t>Tvorog 9% 250 gr</t>
+  </si>
+  <si>
+    <t>00406002001000999</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>Услуги по доставке товаров</t>
+  </si>
+  <si>
+    <t>услуга</t>
+  </si>
+  <si>
+    <t>45000</t>
+  </si>
+  <si>
+    <t>Hojatxona qog'ozi 4 rulon</t>
+  </si>
+  <si>
+    <t>79500</t>
+  </si>
+  <si>
+    <t>Shpaklyovka finish 250 gr</t>
+  </si>
+  <si>
+    <t>71000</t>
+  </si>
+  <si>
+    <t>Мураббо (джем) абрикос 250 gr</t>
+  </si>
+  <si>
+    <t>дона</t>
+  </si>
+  <si>
+    <t>29000</t>
+  </si>
+  <si>
+    <t>Un 1-nav 10 kg</t>
+  </si>
+  <si>
+    <t>BONI bear, qumoq, PP paket 30 g</t>
+  </si>
+  <si>
+    <t>4780101741298</t>
+  </si>
+  <si>
+    <t>01905012001504001</t>
+  </si>
+  <si>
+    <t>63500</t>
+  </si>
+  <si>
+    <t>Сметана 20% 2 kg</t>
+  </si>
+  <si>
+    <t>Shakar 3 кг</t>
+  </si>
+  <si>
+    <t>03402003024000000</t>
+  </si>
+  <si>
+    <t>92000</t>
+  </si>
+  <si>
+    <t>Un oliy nav 1 кг</t>
+  </si>
+  <si>
+    <t>00803001001000000</t>
+  </si>
+  <si>
+    <t>37500</t>
+  </si>
+  <si>
+    <t>Sabzi</t>
+  </si>
+  <si>
+    <t>00706001001000000</t>
+  </si>
+  <si>
+    <t>44500</t>
+  </si>
+  <si>
+    <t>Choynak elektr 0,25 л</t>
+  </si>
+  <si>
+    <t>08516999043000000</t>
+  </si>
+  <si>
+    <t>95000</t>
+  </si>
+  <si>
+    <t>Мураббо (джем) абрикос 400 г</t>
+  </si>
+  <si>
+    <t>69000</t>
+  </si>
+  <si>
+    <t>Лук репчатый</t>
+  </si>
+  <si>
+    <t>55500</t>
+  </si>
+  <si>
+    <t>Nu pogodi, tuxum ifori bilan, PET butilka 400 g.</t>
+  </si>
+  <si>
+    <t>4780035400698</t>
+  </si>
+  <si>
+    <t>61500</t>
+  </si>
+  <si>
+    <t>Sosiska 1 kg</t>
+  </si>
+  <si>
+    <t>Un oliy nav 50 kg qop</t>
+  </si>
+  <si>
+    <t>6500</t>
+  </si>
+  <si>
+    <t>A4 qog'oz 500 varaq</t>
+  </si>
+  <si>
+    <t>04802001006000000</t>
+  </si>
+  <si>
+    <t>74500</t>
+  </si>
+  <si>
+    <t>Idish yuvish vositasi 500 ml</t>
+  </si>
+  <si>
+    <t>03402002001000000</t>
+  </si>
+  <si>
+    <t>kilogramm</t>
+  </si>
+  <si>
+    <t>33000</t>
+  </si>
+  <si>
+    <t>Qahva eriydigan 100 g shisha idishda</t>
+  </si>
+  <si>
+    <t>27000</t>
+  </si>
+  <si>
+    <t>Shpaklyovka finish 20 kg</t>
+  </si>
+  <si>
+    <t>03214001003000000</t>
+  </si>
+  <si>
+    <t>39500</t>
+  </si>
+  <si>
+    <t>Sariyog' 82,5% 5 kg</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>LAL ANAAR, Anorli pet butilka 0.5 l</t>
+  </si>
+  <si>
+    <t>4780053100648</t>
+  </si>
+  <si>
+    <t>02202002005132023</t>
+  </si>
+  <si>
+    <t>38500</t>
+  </si>
+  <si>
+    <t>Gugurt 10 quti</t>
+  </si>
+  <si>
+    <t>03605001001000000</t>
+  </si>
+  <si>
+    <t>Pechenye sutli 3 кг</t>
+  </si>
+  <si>
+    <t>01905012001000000</t>
+  </si>
+  <si>
+    <t>22500</t>
+  </si>
+  <si>
+    <t>Omonхоna, pet butilka 5 l</t>
+  </si>
+  <si>
+    <t>4780167200029</t>
+  </si>
+  <si>
+    <t>02201001001401003</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>Kungaboqar yog'i rafinatsiya 1L</t>
+  </si>
+  <si>
+    <t>01512001001000000</t>
+  </si>
+  <si>
+    <t>litr</t>
+  </si>
+  <si>
+    <t>59500</t>
+  </si>
+  <si>
+    <t>Мош (маш) 2 kg</t>
+  </si>
+  <si>
+    <t>07317001001000000</t>
+  </si>
+  <si>
+    <t>39000</t>
+  </si>
+  <si>
+    <t>Шарбат олма 1 л</t>
+  </si>
+  <si>
+    <t>02009001006000000</t>
+  </si>
+  <si>
+    <t>88000</t>
+  </si>
+  <si>
+    <t>Pomidor</t>
+  </si>
+  <si>
+    <t>00702001001000000</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>Limon</t>
+  </si>
+  <si>
+    <t>Non (patir non)</t>
+  </si>
+  <si>
+    <t>47000</t>
+  </si>
+  <si>
+    <t>Idish yuvish vositasi 0,5 l</t>
+  </si>
+  <si>
+    <t>91000</t>
+  </si>
+  <si>
+    <t>Guruch Devzira 1 kg</t>
+  </si>
+  <si>
+    <t>1006001003000000</t>
+  </si>
+  <si>
+    <t>Neon, Multimeva, PET butilka 0,3 l</t>
+  </si>
+  <si>
+    <t>4780022160529</t>
+  </si>
+  <si>
+    <t>02202002001099001</t>
+  </si>
+  <si>
+    <t>Ko'k choy 95-sort 100 gr</t>
+  </si>
+  <si>
+    <t>00902001001000000</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>Oqartiruvchi vosita 1 l</t>
+  </si>
+  <si>
+    <t>3402001003000000</t>
+  </si>
+  <si>
+    <t>43500</t>
+  </si>
+  <si>
+    <t>Somsa</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>Sement M400 50 kg qop</t>
+  </si>
+  <si>
+    <t>02523002009000000</t>
+  </si>
+  <si>
+    <t>tonna</t>
+  </si>
+  <si>
+    <t>57500</t>
+  </si>
+  <si>
+    <t>Konti, qumoq, glazurlangan, gofra quti 300 gr</t>
+  </si>
+  <si>
+    <t>4780059620201</t>
+  </si>
+  <si>
+    <t>01905012001295006</t>
+  </si>
+  <si>
+    <t>94000</t>
+  </si>
+  <si>
+    <t>Sariyog' 82,5% 200 g</t>
+  </si>
+  <si>
+    <t>53500</t>
+  </si>
+  <si>
+    <t>Mol go'shti lahm</t>
+  </si>
+  <si>
+    <t>55000</t>
+  </si>
+  <si>
+    <t>Grechka 900 gr</t>
+  </si>
+  <si>
+    <t>01104001005000000</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>Вода питьевая негазированная 1,5 L</t>
+  </si>
+  <si>
+    <t>02201001001000000</t>
+  </si>
+  <si>
+    <t>78000</t>
+  </si>
+  <si>
+    <t>Tovuq go'shti (broyler) muzlatilgan</t>
+  </si>
+  <si>
+    <t>00207001009000000</t>
+  </si>
+  <si>
+    <t>Dora, PET idish 500 g</t>
+  </si>
+  <si>
+    <t>4780015352382</t>
+  </si>
+  <si>
+    <t>89500</t>
+  </si>
+  <si>
+    <t>BAHODIR NON, Baxodir Polietilen paket 350 g</t>
+  </si>
+  <si>
+    <t>4780083450072</t>
+  </si>
+  <si>
+    <t>01905002001032005</t>
+  </si>
+  <si>
+    <t>17500</t>
+  </si>
+  <si>
+    <t>Стиральный порошок ручная стирка 450г</t>
+  </si>
+  <si>
+    <t>Daftar 48 varaq katak</t>
+  </si>
+  <si>
+    <t>04820002001000999</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>Вода питьевая негазированная 5 л</t>
+  </si>
+  <si>
+    <t>99500</t>
+  </si>
+  <si>
+    <t>Торнадо, shakarli, sut tamli, PE paket 180 gr</t>
+  </si>
+  <si>
+    <t>4780023460284</t>
+  </si>
+  <si>
+    <t>34500</t>
+  </si>
+  <si>
+    <t>Майонез 67% 0,25 л</t>
+  </si>
+  <si>
+    <t>02103002004000000</t>
+  </si>
+  <si>
+    <t>73000</t>
+  </si>
+  <si>
+    <t>МузА, Konditer mahsuloti, PE qadoqda 250 g</t>
+  </si>
+  <si>
+    <t>4780010051938</t>
+  </si>
+  <si>
+    <t>01905012001230023</t>
+  </si>
+  <si>
+    <t>33500</t>
+  </si>
+  <si>
+    <t>Sirka 9% 0,5 l</t>
+  </si>
+  <si>
+    <t>02209001001000000</t>
+  </si>
+  <si>
+    <t>PegAs, suyuq sovun PET butilka 370 g.</t>
+  </si>
+  <si>
+    <t>4780041180522</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>Kompot olcha 3 l</t>
+  </si>
+  <si>
+    <t>02202004004000000</t>
+  </si>
+  <si>
+    <t>Ombor ijarasi</t>
+  </si>
+  <si>
+    <t>10106002001000000</t>
+  </si>
+  <si>
+    <t>56500</t>
+  </si>
+  <si>
+    <t>Tomat pastasi 800 gr shisha</t>
+  </si>
+  <si>
+    <t>2002001003000000</t>
+  </si>
+  <si>
+    <t>49500</t>
+  </si>
+  <si>
+    <t>Сыр твердый 45% весовой</t>
+  </si>
+  <si>
+    <t>00406001001000000</t>
+  </si>
+  <si>
+    <t>35500</t>
+  </si>
+  <si>
+    <t>Ko'k choy 95-sort 250 gr</t>
+  </si>
+  <si>
+    <t>Ketchup 3 кг</t>
+  </si>
+  <si>
+    <t>02103004001000999</t>
+  </si>
+  <si>
+    <t>97000</t>
+  </si>
+  <si>
+    <t>Sosiska 1 кг</t>
+  </si>
+  <si>
+    <t>01601002002000000</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>93000</t>
+  </si>
+  <si>
+    <t>7UP, Alyuminiy banka 0,449 l</t>
+  </si>
+  <si>
+    <t>4780022621747</t>
+  </si>
+  <si>
+    <t>24500</t>
+  </si>
+  <si>
+    <t>Сметана 20% 400г</t>
+  </si>
+  <si>
+    <t>00403999008000000</t>
+  </si>
+  <si>
+    <t>Atir sovun 90 g</t>
+  </si>
+  <si>
+    <t>03401001001000000</t>
+  </si>
+  <si>
+    <t>Колбаса варёная весовая</t>
+  </si>
+  <si>
+    <t>Нон буханка 500 г</t>
+  </si>
+  <si>
+    <t>01905002007000000</t>
+  </si>
+  <si>
+    <t>23500</t>
+  </si>
+  <si>
+    <t>Tuxum C1 10 dona</t>
+  </si>
+  <si>
+    <t>00407001001000000</t>
+  </si>
+  <si>
+    <t>83000</t>
+  </si>
+  <si>
+    <t>Ручка шариковая синяя</t>
+  </si>
+  <si>
+    <t>09608001001000000</t>
+  </si>
+  <si>
+    <t>38000</t>
+  </si>
+  <si>
+    <t>Asal tabiiy 3 кг</t>
+  </si>
+  <si>
+    <t>00409001001000999</t>
+  </si>
+  <si>
+    <t>70000</t>
+  </si>
+  <si>
+    <t>Shakar-rafinad 1 кг</t>
+  </si>
+  <si>
+    <t>01701001002000000</t>
+  </si>
+  <si>
+    <t>Choynak elektr 1,7 l</t>
+  </si>
+  <si>
+    <t>31500</t>
+  </si>
+  <si>
+    <t>Газированный напиток лимон 1.5 л</t>
+  </si>
+  <si>
+    <t>02202002001000000</t>
+  </si>
+  <si>
+    <t>52500</t>
+  </si>
+  <si>
+    <t>Azov, Raxat-lukum yong’oq 160 gr quti</t>
+  </si>
+  <si>
+    <t>4620004255525</t>
+  </si>
+  <si>
+    <t>01704001018001005</t>
+  </si>
+  <si>
+    <t>23000</t>
+  </si>
+  <si>
+    <t>Moya Semya, Olmali miks, Tetra pak 1,93 l</t>
+  </si>
+  <si>
+    <t>4650075421215</t>
+  </si>
+  <si>
+    <t>Kompot olcha 3 l banka</t>
+  </si>
+  <si>
+    <t>00902001002000000</t>
+  </si>
+  <si>
+    <t>67000</t>
+  </si>
+  <si>
+    <t>Folga alyuminiy 10 m</t>
+  </si>
+  <si>
+    <t>07607001001000000</t>
+  </si>
+  <si>
+    <t>No'xat 1 kg</t>
+  </si>
+  <si>
+    <t>00708001001000000</t>
+  </si>
+  <si>
+    <t>Банан</t>
+  </si>
+  <si>
+    <t>Shokolad sutli 90 g</t>
+  </si>
+  <si>
+    <t>01806001008000000</t>
+  </si>
+  <si>
+    <t>Kir yuvish kukuni avtomat 3 kg</t>
+  </si>
+  <si>
+    <t>03402003002000000</t>
+  </si>
+  <si>
+    <t>20500</t>
+  </si>
+  <si>
+    <t>Шарбат олма 0,25 л</t>
+  </si>
+  <si>
+    <t>Keramik plitka pol uchun</t>
+  </si>
+  <si>
+    <t>06905001001000999</t>
+  </si>
+  <si>
+    <t>kv. metr</t>
+  </si>
+  <si>
+    <t>Мош (маш) 1кг</t>
+  </si>
+  <si>
+    <t>79000</t>
+  </si>
+  <si>
+    <t>Сахар-песок 50 кг мешок</t>
+  </si>
+  <si>
+    <t>28500</t>
+  </si>
+  <si>
+    <t>Сут 3,2% 0,5 l</t>
+  </si>
+  <si>
+    <t>00401001001000000</t>
+  </si>
+  <si>
+    <t>48500</t>
+  </si>
+  <si>
+    <t>Paxta yog'i 1 l</t>
+  </si>
+  <si>
+    <t>Tuz yodlangan 1 kg</t>
+  </si>
+  <si>
+    <t>02501001007000000</t>
+  </si>
+  <si>
+    <t>Paxta yog'i 0,25 л</t>
+  </si>
+  <si>
+    <t>01512002001000000</t>
+  </si>
+  <si>
+    <t>Makaron spagetti 400g</t>
+  </si>
+  <si>
+    <t>94500</t>
+  </si>
+  <si>
+    <t>Effect, suyuq sovun Polietilen butilka 0,5 l.</t>
+  </si>
+  <si>
+    <t>4780016610023</t>
+  </si>
+  <si>
+    <t>03401001002060003</t>
+  </si>
+  <si>
+    <t>63000</t>
+  </si>
+  <si>
+    <t>Шампунь 0,5 l</t>
+  </si>
+  <si>
+    <t>03305005001000000</t>
+  </si>
+  <si>
+    <t>Baliq konservasi (sardina) 240 g</t>
+  </si>
+  <si>
+    <t>Bolalar tagligi (podguznik) 4-o'lcham 50 dona</t>
+  </si>
+  <si>
+    <t>09619002004000000</t>
+  </si>
+  <si>
+    <t>45500</t>
+  </si>
+  <si>
+    <t>Краска водоэмульсионная белая 3 кг</t>
+  </si>
+  <si>
+    <t>03209001005000000</t>
+  </si>
+  <si>
+    <t>98500</t>
+  </si>
+  <si>
+    <t>Grechka 10 kg</t>
+  </si>
+  <si>
+    <t>Olma</t>
+  </si>
+  <si>
+    <t>00808001001000000</t>
+  </si>
+  <si>
+    <t>Шампунь 400 мл</t>
+  </si>
+  <si>
+    <t>Чай черный пакетированный 100 пак.</t>
+  </si>
+  <si>
+    <t>41500</t>
+  </si>
+  <si>
+    <t>Tish cho'tkasi o'rtacha qattiqlik</t>
+  </si>
+  <si>
+    <t>53000</t>
+  </si>
+  <si>
+    <t>Tomat pastasi 5 kg</t>
+  </si>
+  <si>
+    <t>02002001003000000</t>
+  </si>
+  <si>
+    <t>Makaron spagetti 250 gr</t>
+  </si>
+  <si>
+    <t>01902001009000999</t>
+  </si>
+  <si>
+    <t>5500</t>
+  </si>
+  <si>
+    <t>Mineral suv gazli 1,5L</t>
+  </si>
+  <si>
+    <t>02201002001000000</t>
+  </si>
+  <si>
+    <t>Qatiq 2,5% 450 g</t>
+  </si>
+  <si>
+    <t>03917001001000000</t>
+  </si>
+  <si>
+    <t>Мыло хозяйственное 72% 200г</t>
+  </si>
+  <si>
+    <t>03401001004000000</t>
+  </si>
+  <si>
+    <t>87500</t>
+  </si>
+  <si>
+    <t>Мыло хозяйственное 72% 5 kg</t>
+  </si>
+  <si>
+    <t>03401001004000999</t>
+  </si>
+  <si>
+    <t>86500</t>
+  </si>
+  <si>
+    <t>Atir sovun 250 gr</t>
+  </si>
+  <si>
+    <t>Pechenye sutli 300 gr</t>
+  </si>
+  <si>
+    <t>8000</t>
+  </si>
+  <si>
+    <t>Mega Xrust, unli, yog’li, kabob tami bilan, PP paket 17 gr</t>
+  </si>
+  <si>
+    <t>4780041020606</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>Стиральный порошок ручная стирка 5 kg</t>
+  </si>
+  <si>
+    <t>Manti 1 porsiya</t>
+  </si>
+  <si>
+    <t>88500</t>
+  </si>
+  <si>
+    <t>Рис круглозерный 3 кг</t>
+  </si>
+  <si>
+    <t>01805001001000000</t>
+  </si>
+  <si>
+    <t>80500</t>
+  </si>
+  <si>
+    <t>Gips shtukaturka 30 kg</t>
+  </si>
+  <si>
+    <t>Oqartiruvchi vosita 1,5 L</t>
+  </si>
+  <si>
+    <t>03402001003000000</t>
+  </si>
+  <si>
+    <t>Suli yormasi 10 kg</t>
+  </si>
+  <si>
+    <t>90500</t>
+  </si>
+  <si>
+    <t>Bodring</t>
+  </si>
+  <si>
+    <t>00707001001000000</t>
+  </si>
+  <si>
+    <t>11500</t>
+  </si>
+  <si>
+    <t>Масло подсолнечное 5л</t>
+  </si>
+  <si>
+    <t>76000</t>
+  </si>
+  <si>
+    <t>Труба ПВХ 110 мм</t>
+  </si>
+  <si>
+    <t>3917001001000000</t>
+  </si>
+  <si>
+    <t>м</t>
+  </si>
+  <si>
+    <t>Kir yuvish kukuni avtomat 3 кг</t>
+  </si>
+  <si>
+    <t>Салфетки бумажные 100 шт</t>
+  </si>
+  <si>
+    <t>упак</t>
+  </si>
+  <si>
+    <t>Baliq konservasi (sardina) 2 kg</t>
+  </si>
+  <si>
+    <t>01604001001000000</t>
+  </si>
+  <si>
+    <t>62500</t>
+  </si>
+  <si>
+    <t>Asal tabiiy 500 gr</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>Palov 1 porsiya (oshxona)</t>
+  </si>
+  <si>
+    <t>Ketchup 500 g</t>
+  </si>
+  <si>
+    <t>02103004001000000</t>
+  </si>
+  <si>
+    <t>25500</t>
+  </si>
+  <si>
+    <t>Майонез 67% 400 мл</t>
+  </si>
+  <si>
+    <t>Sirka 9% 0,25 л</t>
+  </si>
+  <si>
+    <t>Shakar 1 kg qadoqlangan</t>
+  </si>
+  <si>
+    <t>Sostoned, alyumin banka 0.33 l</t>
+  </si>
+  <si>
+    <t>8594196130549</t>
+  </si>
+  <si>
+    <t>56000</t>
+  </si>
+  <si>
+    <t>Guruch Devzira 250 gr</t>
+  </si>
+  <si>
+    <t>01006001003000000</t>
+  </si>
+  <si>
+    <t>62000</t>
+  </si>
+  <si>
+    <t>Qatiq 2,5% 3 кг</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>Сахар-песок 10 kg</t>
+  </si>
+  <si>
+    <t>96500</t>
+  </si>
+  <si>
+    <t>Краска водоэмульсионная белая 10 кг</t>
+  </si>
+  <si>
+    <t>03209001005000999</t>
+  </si>
+  <si>
+    <t>67500</t>
+  </si>
+  <si>
+    <t>Kakao kukuni 100 gr</t>
+  </si>
+  <si>
+    <t>66500</t>
+  </si>
+  <si>
+    <t>POKIZA, kukunsimon, oqartirish vositasi, kart. quti 120 g.</t>
+  </si>
+  <si>
+    <t>4780031390092</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>Tvorog 9% 200 gr</t>
+  </si>
+  <si>
+    <t>Мука пшеничная в/с 2 кг</t>
+  </si>
+  <si>
+    <t>31000</t>
+  </si>
+  <si>
+    <t>Tish pastasi 0,25 л</t>
+  </si>
+  <si>
+    <t>44000</t>
+  </si>
+  <si>
+    <t>Gips shtukaturka 5 kg</t>
+  </si>
+  <si>
+    <t>01701001001000000</t>
+  </si>
+  <si>
+    <t>Shokolad sutli 250 gr</t>
+  </si>
+  <si>
+    <t>Нон буханка 1 кг</t>
+  </si>
+  <si>
+    <t>87000</t>
+  </si>
+  <si>
+    <t>Raffaello, confetteria 80g</t>
+  </si>
+  <si>
+    <t>4607086410288</t>
+  </si>
+  <si>
+    <t>01806003001026001</t>
+  </si>
+  <si>
+    <t>58000</t>
+  </si>
+  <si>
+    <t>Shakar-rafinad 500 gr</t>
+  </si>
+  <si>
+    <t>Kungaboqar yog'i rafinatsiya 0,5 l</t>
+  </si>
+  <si>
+    <t>Сут 3,2% 1 л</t>
+  </si>
+  <si>
+    <t>00201001001000000</t>
+  </si>
+  <si>
+    <t>93500</t>
+  </si>
+  <si>
+    <t>New Bek Best Cleaner, xo’jalik uchun pet baklajka 3000 gr.</t>
+  </si>
+  <si>
+    <t>4780088820139</t>
+  </si>
+  <si>
+    <t>03401001002321001</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>Qahva eriydigan 1 кг</t>
+  </si>
+  <si>
+    <t>02101001001000000</t>
+  </si>
+  <si>
+    <t>Tish pastasi 100 ml</t>
+  </si>
+  <si>
+    <t>03306001001000999</t>
+  </si>
+  <si>
+    <t>Tuz yodlangan 1 кг</t>
+  </si>
+  <si>
+    <t>Батарейка AA 2 шт</t>
+  </si>
+  <si>
+    <t>No'xat 1 кг</t>
+  </si>
+  <si>
+    <t>Suli yormasi 500 gr</t>
+  </si>
+  <si>
+    <t>Вермишель 5 кг</t>
+  </si>
+  <si>
+    <t>01902001009000000</t>
+  </si>
+  <si>
+    <t>Конфеты шоколадные весовые</t>
+  </si>
+  <si>
+    <t>01806003001000000</t>
   </si>
 </sst>
 </file>
@@ -717,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1200,6 +2325,2709 @@
         <v>107</v>
       </c>
     </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" t="s">
+        <v>113</v>
+      </c>
+      <c r="E30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>120</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" t="s">
+        <v>122</v>
+      </c>
+      <c r="E33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" t="s">
+        <v>110</v>
+      </c>
+      <c r="E34" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" t="s">
+        <v>128</v>
+      </c>
+      <c r="E35" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>132</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" t="s">
+        <v>110</v>
+      </c>
+      <c r="E37" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>137</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" t="s">
+        <v>122</v>
+      </c>
+      <c r="E39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" t="s">
+        <v>110</v>
+      </c>
+      <c r="E40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>142</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>143</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" t="s">
+        <v>110</v>
+      </c>
+      <c r="E42" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>146</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D43" t="s">
+        <v>122</v>
+      </c>
+      <c r="E43" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D44" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>152</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D45" t="s">
+        <v>110</v>
+      </c>
+      <c r="E45" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>155</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" t="s">
+        <v>135</v>
+      </c>
+      <c r="E46" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>157</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" t="s">
+        <v>74</v>
+      </c>
+      <c r="E47" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>159</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48" t="s">
+        <v>110</v>
+      </c>
+      <c r="E48" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>162</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" t="s">
+        <v>122</v>
+      </c>
+      <c r="E49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>163</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" t="s">
+        <v>122</v>
+      </c>
+      <c r="E50" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D51" t="s">
+        <v>110</v>
+      </c>
+      <c r="E51" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>168</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D52" t="s">
+        <v>170</v>
+      </c>
+      <c r="E52" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>172</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D53" t="s">
+        <v>110</v>
+      </c>
+      <c r="E53" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>174</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D54" t="s">
+        <v>170</v>
+      </c>
+      <c r="E54" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>177</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" t="s">
+        <v>110</v>
+      </c>
+      <c r="E55" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>179</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D56" t="s">
+        <v>110</v>
+      </c>
+      <c r="E56" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>183</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D57" t="s">
+        <v>110</v>
+      </c>
+      <c r="E57" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>185</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D58" t="s">
+        <v>110</v>
+      </c>
+      <c r="E58" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>188</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D59" t="s">
+        <v>110</v>
+      </c>
+      <c r="E59" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>192</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D60" t="s">
+        <v>194</v>
+      </c>
+      <c r="E60" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>196</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D61" t="s">
+        <v>74</v>
+      </c>
+      <c r="E61" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>199</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D62" t="s">
+        <v>113</v>
+      </c>
+      <c r="E62" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>202</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D63" t="s">
+        <v>122</v>
+      </c>
+      <c r="E63" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>205</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64" t="s">
+        <v>122</v>
+      </c>
+      <c r="E64" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>206</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D65" t="s">
+        <v>110</v>
+      </c>
+      <c r="E65" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>208</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D66" t="s">
+        <v>170</v>
+      </c>
+      <c r="E66" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>210</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D67" t="s">
+        <v>110</v>
+      </c>
+      <c r="E67" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>212</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D68" t="s">
+        <v>110</v>
+      </c>
+      <c r="E68" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>215</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D69" t="s">
+        <v>110</v>
+      </c>
+      <c r="E69" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>218</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D70" t="s">
+        <v>194</v>
+      </c>
+      <c r="E70" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>221</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D71" t="s">
+        <v>110</v>
+      </c>
+      <c r="E71" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>223</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D72" t="s">
+        <v>225</v>
+      </c>
+      <c r="E72" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>227</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D73" t="s">
+        <v>110</v>
+      </c>
+      <c r="E73" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>231</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74" t="s">
+        <v>110</v>
+      </c>
+      <c r="E74" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>233</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D75" t="s">
+        <v>122</v>
+      </c>
+      <c r="E75" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>235</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D76" t="s">
+        <v>110</v>
+      </c>
+      <c r="E76" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>238</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D77" t="s">
+        <v>194</v>
+      </c>
+      <c r="E77" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>241</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D78" t="s">
+        <v>122</v>
+      </c>
+      <c r="E78" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>243</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79" t="s">
+        <v>110</v>
+      </c>
+      <c r="E79" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>246</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D80" t="s">
+        <v>110</v>
+      </c>
+      <c r="E80" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>250</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D81" t="s">
+        <v>170</v>
+      </c>
+      <c r="E81" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>251</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D82" t="s">
+        <v>110</v>
+      </c>
+      <c r="E82" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>254</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D83" t="s">
+        <v>194</v>
+      </c>
+      <c r="E83" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>256</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D84" t="s">
+        <v>110</v>
+      </c>
+      <c r="E84" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>259</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D85" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>262</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D86" t="s">
+        <v>110</v>
+      </c>
+      <c r="E86" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>266</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D87" t="s">
+        <v>194</v>
+      </c>
+      <c r="E87" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>268</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D88" t="s">
+        <v>110</v>
+      </c>
+      <c r="E88" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>271</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D89" t="s">
+        <v>194</v>
+      </c>
+      <c r="E89" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>273</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D90" t="s">
+        <v>170</v>
+      </c>
+      <c r="E90" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>276</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D91" t="s">
+        <v>110</v>
+      </c>
+      <c r="E91" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>279</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D92" t="s">
+        <v>113</v>
+      </c>
+      <c r="E92" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>282</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D93" t="s">
+        <v>110</v>
+      </c>
+      <c r="E93" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>283</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D94" t="s">
+        <v>110</v>
+      </c>
+      <c r="E94" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>286</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D95" t="s">
+        <v>113</v>
+      </c>
+      <c r="E95" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>76</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D96" t="s">
+        <v>122</v>
+      </c>
+      <c r="E96" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>290</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D97" t="s">
+        <v>110</v>
+      </c>
+      <c r="E97" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>293</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D98" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>295</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D99" t="s">
+        <v>110</v>
+      </c>
+      <c r="E99" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>297</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D100" t="s">
+        <v>74</v>
+      </c>
+      <c r="E100" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>298</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D101" t="s">
+        <v>135</v>
+      </c>
+      <c r="E101" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>301</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D102" t="s">
+        <v>110</v>
+      </c>
+      <c r="E102" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>304</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D103" t="s">
+        <v>8</v>
+      </c>
+      <c r="E103" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>307</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D104" t="s">
+        <v>110</v>
+      </c>
+      <c r="E104" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>310</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D105" t="s">
+        <v>110</v>
+      </c>
+      <c r="E105" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>312</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D106" t="s">
+        <v>110</v>
+      </c>
+      <c r="E106" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>314</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D107" t="s">
+        <v>194</v>
+      </c>
+      <c r="E107" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>317</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D108" t="s">
+        <v>110</v>
+      </c>
+      <c r="E108" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>321</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D109" t="s">
+        <v>110</v>
+      </c>
+      <c r="E109" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>323</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D110" t="s">
+        <v>194</v>
+      </c>
+      <c r="E110" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>326</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D111" t="s">
+        <v>110</v>
+      </c>
+      <c r="E111" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>328</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D112" t="s">
+        <v>122</v>
+      </c>
+      <c r="E112" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>330</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D113" t="s">
+        <v>74</v>
+      </c>
+      <c r="E113" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>331</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D114" t="s">
+        <v>170</v>
+      </c>
+      <c r="E114" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>333</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D115" t="s">
+        <v>194</v>
+      </c>
+      <c r="E115" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>336</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D116" t="s">
+        <v>225</v>
+      </c>
+      <c r="E116" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>337</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D117" t="s">
+        <v>339</v>
+      </c>
+      <c r="E117" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>340</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D118" t="s">
+        <v>74</v>
+      </c>
+      <c r="E118" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>342</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D119" t="s">
+        <v>74</v>
+      </c>
+      <c r="E119" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>344</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D120" t="s">
+        <v>135</v>
+      </c>
+      <c r="E120" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>347</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D121" t="s">
+        <v>194</v>
+      </c>
+      <c r="E121" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>348</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D122" t="s">
+        <v>110</v>
+      </c>
+      <c r="E122" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>350</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D123" t="s">
+        <v>194</v>
+      </c>
+      <c r="E123" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>352</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D124" t="s">
+        <v>110</v>
+      </c>
+      <c r="E124" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>354</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D125" t="s">
+        <v>110</v>
+      </c>
+      <c r="E125" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>358</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D126" t="s">
+        <v>194</v>
+      </c>
+      <c r="E126" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>360</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D127" t="s">
+        <v>110</v>
+      </c>
+      <c r="E127" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>361</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D128" t="s">
+        <v>110</v>
+      </c>
+      <c r="E128" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>364</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D129" t="s">
+        <v>74</v>
+      </c>
+      <c r="E129" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>367</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D130" t="s">
+        <v>110</v>
+      </c>
+      <c r="E130" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>368</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D131" t="s">
+        <v>122</v>
+      </c>
+      <c r="E131" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>370</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D132" t="s">
+        <v>194</v>
+      </c>
+      <c r="E132" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>371</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D133" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>373</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D134" t="s">
+        <v>110</v>
+      </c>
+      <c r="E134" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>375</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D135" t="s">
+        <v>110</v>
+      </c>
+      <c r="E135" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>377</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D136" t="s">
+        <v>110</v>
+      </c>
+      <c r="E136" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>380</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D137" t="s">
+        <v>194</v>
+      </c>
+      <c r="E137" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>382</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D138" t="s">
+        <v>110</v>
+      </c>
+      <c r="E138" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>384</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D139" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>387</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D140" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>390</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D141" t="s">
+        <v>110</v>
+      </c>
+      <c r="E141" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>391</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D142" t="s">
+        <v>110</v>
+      </c>
+      <c r="E142" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>393</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D143" t="s">
+        <v>110</v>
+      </c>
+      <c r="E143" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>396</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D144" t="s">
+        <v>170</v>
+      </c>
+      <c r="E144" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>397</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D145" t="s">
+        <v>110</v>
+      </c>
+      <c r="E145" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>399</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D146" t="s">
+        <v>110</v>
+      </c>
+      <c r="E146" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>402</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D147" t="s">
+        <v>170</v>
+      </c>
+      <c r="E147" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>403</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D148" t="s">
+        <v>113</v>
+      </c>
+      <c r="E148" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>405</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D149" t="s">
+        <v>110</v>
+      </c>
+      <c r="E149" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>407</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D150" t="s">
+        <v>122</v>
+      </c>
+      <c r="E150" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>410</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D151" t="s">
+        <v>34</v>
+      </c>
+      <c r="E151" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>412</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="D152" t="s">
+        <v>414</v>
+      </c>
+      <c r="E152" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>415</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D153" t="s">
+        <v>170</v>
+      </c>
+      <c r="E153" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>416</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D154" t="s">
+        <v>417</v>
+      </c>
+      <c r="E154" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>418</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D155" t="s">
+        <v>110</v>
+      </c>
+      <c r="E155" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>421</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D156" t="s">
+        <v>110</v>
+      </c>
+      <c r="E156" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>423</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D157" t="s">
+        <v>110</v>
+      </c>
+      <c r="E157" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>424</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D158" t="s">
+        <v>110</v>
+      </c>
+      <c r="E158" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>427</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D159" t="s">
+        <v>8</v>
+      </c>
+      <c r="E159" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>428</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D160" t="s">
+        <v>194</v>
+      </c>
+      <c r="E160" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>429</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D161" t="s">
+        <v>110</v>
+      </c>
+      <c r="E161" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>430</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D162" t="s">
+        <v>110</v>
+      </c>
+      <c r="E162" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>433</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D163" t="s">
+        <v>110</v>
+      </c>
+      <c r="E163" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>436</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D164" t="s">
+        <v>110</v>
+      </c>
+      <c r="E164" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>438</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D165" t="s">
+        <v>74</v>
+      </c>
+      <c r="E165" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>440</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D166" t="s">
+        <v>74</v>
+      </c>
+      <c r="E166" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>443</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D167" t="s">
+        <v>110</v>
+      </c>
+      <c r="E167" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>445</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D168" t="s">
+        <v>110</v>
+      </c>
+      <c r="E168" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>448</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D169" t="s">
+        <v>110</v>
+      </c>
+      <c r="E169" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>449</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D170" t="s">
+        <v>74</v>
+      </c>
+      <c r="E170" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>451</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D171" t="s">
+        <v>110</v>
+      </c>
+      <c r="E171" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>453</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D172" t="s">
+        <v>170</v>
+      </c>
+      <c r="E172" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>455</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D173" t="s">
+        <v>170</v>
+      </c>
+      <c r="E173" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>456</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D174" t="s">
+        <v>135</v>
+      </c>
+      <c r="E174" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>458</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="D175" t="s">
+        <v>110</v>
+      </c>
+      <c r="E175" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>462</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D176" t="s">
+        <v>110</v>
+      </c>
+      <c r="E176" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>463</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D177" t="s">
+        <v>194</v>
+      </c>
+      <c r="E177" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>464</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D178" t="s">
+        <v>135</v>
+      </c>
+      <c r="E178" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>467</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D179" t="s">
+        <v>110</v>
+      </c>
+      <c r="E179" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>471</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D180" t="s">
+        <v>110</v>
+      </c>
+      <c r="E180" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>473</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D181" t="s">
+        <v>110</v>
+      </c>
+      <c r="E181" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>475</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D182" t="s">
+        <v>110</v>
+      </c>
+      <c r="E182" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>476</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D183" t="s">
+        <v>417</v>
+      </c>
+      <c r="E183" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>477</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D184" t="s">
+        <v>122</v>
+      </c>
+      <c r="E184" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>478</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D185" t="s">
+        <v>110</v>
+      </c>
+      <c r="E185" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>479</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D186" t="s">
+        <v>74</v>
+      </c>
+      <c r="E186" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>481</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D187" t="s">
+        <v>74</v>
+      </c>
+      <c r="E187" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
